--- a/PTBR/Lang/PTBR/Game/List.xlsx
+++ b/PTBR/Lang/PTBR/Game/List.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Um,Uma</t>
+          <t>uma ,um</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -508,12 +508,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alpha 12.1</t>
+          <t>EA 23.313</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Janeiro,Fevereiro,Março,Abril,Maio,Junho,Julho,Agosto,Setembro,Outubro,Novembro,Dezembro</t>
+          <t>Janeiro, Fevereiro, Março, Abril, Maio, Junho, Julho, Agosto, Setembro, Outubro, Novembro, Dezembro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Menina,Menina,Menino</t>
+          <t>garota,garota,garoto</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Irmão,Mano,Garoto</t>
+          <t>irmão,maninho,rapaz</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Irmã,Mana,Garota</t>
+          <t>irmã,maninha,moça</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>...,Umimyaa,Não Consigo Dormir Esta Noite,Porquê eu fui brigar…,Era só pra cortar uma madeia…,Antes morto do que sem vida, Prefiro morrer do que perder a vida</t>
+          <t>...,Umimyaa,Não consigo dormir hoje</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Inimigo,Ódio,Irritante,Normal,Aprovado,Amigável,Respeitado,Íntimo,Afetuoso,Amor,Amor Amor,Amor Amor Amor,♥</t>
+          <t>Inimigo,Ódio,Irritante,Normal,Aprovado,Amistoso,Respeitado,Íntimo,Afeição,*Amor*,*Amor Amor*,*Amor Amor Amor*,♥</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Poção Malhada,Poção Nublada,Poção Clara,Poção Turva,Poção Pálida,Poção Pegajosa,Poção Borbulhante</t>
+          <t>poção manchada,poção turva,poção cristalina,poção escura,poção pálida,poção grudenta,poção borbulhante</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pergaminho Antigo,Pergaminho Estranho,Pergaminho Rúnico,Pergaminho Longo,Pergaminho Rasgado</t>
+          <t>pergaminho velho,pergaminho estranho,pergaminho rúnico,pergaminho comprido,pergaminho rasgado</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Livro Suspeito,Livro Fino,Livro Leve,Livro Atraente,Livro Chamativo,Livro Brilhante,Livro Preocupante,Livro Majestoso,Livro Pesado</t>
+          <t>livro suspeito,livro fino,livro leve,livro atraente,livro vistoso,livro reluzente,livro preocupante,livro majestoso,livro pesado</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tomo Antigo,Tomo Estranho,Tomo Rúnico,Tomo Grosso,Tomo Majestoso</t>
+          <t>tomo velho,tomo estranho,tomo rúnico,tomo grosso,tomo majestoso</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bastão Curto,Bastão Longo,Bastão Torto,Bastão Grosso,Bastão Fino,Bastão Pesado,Bastão Incomum,Bastão Elegante,Bastão Simples</t>
+          <t>varinha curta,varinha comprida,varinha torta,varinha grossa,varinha fina,varinha pesada,varinha esquisita,varinha chique,varinha simples</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Armadilha Desconhecida</t>
+          <t>armadilha desconhecida</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>*Crunch*,*Scritch*,*Kisssh*,*Thudd*,*Clump*</t>
+          <t>*nham*,*ranh*,*beij*,*TUM*,*toc*</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>*Drip*,*Sip*,*Drizzle*,*Splash*,*Kissh*</t>
+          <t>*tlim*,*gole*,*fio fio*,*splash*,*beij*</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>*Pling♪*,*Zing♪*,*Plunk♪*,*Chika Chika♪*,*Ta Ra Ra♪*</t>
+          <t>*pling♪*,*zin♪*,*plun♪*,*tic tic tic♪*,*lá rá rá♪*</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sem Chance,Forte,Briga Justa,Fraco,Muito Fraco</t>
+          <t>Fora do seu alcance,Formidável,Justo,Fácil,Muito fácil</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>corta(-s),corta(-s),corta(-s),corta(-s)</t>
+          <t>talha,talha,talha,talha</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>estoca(-s),estoca(-s),estoca(-s),estoca(-s)</t>
+          <t>apunhala,apunhala,apunhala,apunhala</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>esmaga(-s),esmaga(-s),esmaga(-s),esmaga(-s)</t>
+          <t>esmaga,esmaga,esmaga,esmaga</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>eletrocuta(-s),eletrocuta(-s),eletrocuta(-s),eletrocuta(-s)</t>
+          <t>zapa,zapa,zapa,zapa</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>dispara(-s),dispara(-s),dispara(-s),dispara(-s)</t>
+          <t>dispara,dispara,dispara,dispara</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>soca(-s),soca(-s),soca(-s),soca(-s),mão</t>
+          <t>soca,soca,soca,soca,mão</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>chuta(-s),chuta(-s),chuta(-s),chuta(-s),perna</t>
+          <t>chuta,chuta,chuta,chuta,perna</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>arranha(-s),arranha(-s),arranha(-s),arranha(-s),garra</t>
+          <t>arranha com a garra,arranha com a garra,arranha com a garra,arranha com a garra,garra</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>morde(-s),morde(-s),morde(-s),morde(-s),presa</t>
+          <t>morde,morde,morde,morde,presa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Espalhar(es) Esporos Em,Espalhar(es) Esporos Em,Espalhar(es) Esporos Em,Espalhar(es) Esporos Em,Esporos</t>
+          <t>espalha esporos em,espalha esporos em,espalha esporos em,espalha esporos em,esporos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>encara(-s),encara(-s),encara(-s),encara(-s),olho</t>
+          <t>encara,encara,encara,encara,olho</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pica(-s),pica(-s),pica(-s),pica(-s),agulha</t>
+          <t>fere com o ferrão,fere com o ferrão,fere com o ferrão,fere com o ferrão,agulha</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>toca(-s),toca(-s),toca(-s),toca(-s),mão</t>
+          <t>toca,toca,toca,toca,mão</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enfurecido,Descontente,Mal-Humorado,Calmo,Satisfeito,Encantado,Exultante</t>
+          <t>Enfurecido,Descontente,Mal-humorado,Calmo,Satisfeito,Encantado,Em Êxtase</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Campo De Neve</t>
+          <t>Campo Nevado</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Leito Marinho</t>
+          <t>Leito do Mar</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sala</t>
+          <t>Cômodo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mano</t>
+          <t>Onii</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mana</t>
+          <t>Onee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Irmão♪,Irmão-chan!,Irmãoichan♪,Irmão-chan,Irmão-chan?,Irmão-chan!?</t>
+          <t>Onii♪,Onii-chan!,Oniichan♪,Onii-chan,Onii-chan?,Onii-chan!?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Irmã♪,Irmã-chan!,Irmãichan♪,Irmã-chan,Irmã-chan?,Irmã-chan!?</t>
+          <t>Onee♪,Onee-chan!,Oneechan♪,One-chan,One-chan?,One-chan!?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Conhecido,Vizinho,Amigo,Gato,Cachorro,Leão-Marinho Glutão,Putit,Colega,Frango,Mascote</t>
+          <t>conhecido,vizinho,amigo,gato,cão,leão-marinho guloso,putit,colega,frango,bicho</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Amigo,Parente,Amante,Irmã,Irmão,Esposa,Chefe,Noiva,Querido,Mamãe,Papai,Gato,Criança</t>
+          <t>amigo,pais,amor,irmã,irmão,esposa,chefe,noiva,noivinho,mãe,pai,gato,filho</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Amigo,Magnata,Nobre,Comerciante,Erudito,Aventureiro,Contrabandista,Revendedor</t>
+          <t>amigo,magnata,nobre,mercador,estudioso,aventureiro,mercador negro,traficante</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nenhum,Normal,Forte,Excelente,Imune,Imune+</t>
+          <t>Nada,Normal,Forte,Soberbo,Imunidade,Imunidade+</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Nenhum,Fraqueza,Defeito</t>
+          <t>Nada,Fraqueza,Defeito</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Escolha Um Gênero,,,Lista De Gêneros</t>
+          <t>Escolha o gênero,,,Lista de gêneros</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Escolha Uma Classe,,,Lista De Classes</t>
+          <t>Escolha a classe,,,Lista de classes</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Escolha Uma Raça,,,Lista De Raças</t>
+          <t>Escolha a raça,,,Lista de raças</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Escolha Um Apelido,,,Lista De Apelidos</t>
+          <t>Escolha o apelido,,,Lista de apelidos</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Escolha Uma Faixa Etária,,,Lista De Faixas Etárias</t>
+          <t>Escolha a faixa de idade,,,Lista de faixas de idade</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Escolha Um Prólogo,,,Lista De Prólogos</t>
+          <t>Escolha o prólogo,,,Lista de prólogos</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Escolha Um Local De Portal,,,Nome Do Local</t>
+          <t>Escolha o local do portal,,,Nome do Local</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Escolha Um Local De Retorno,,,Nome Do Local,Nível De Retorno</t>
+          <t>Escolha o local de retorno,,,Nome do Local,Nível de retorno</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Escolha Um Encantamento Para Extrair,,,Nome Do Encantamento,Nível</t>
+          <t>Escolha o encantamento para extrair,,,Nome do Encantamento,Nível</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Escolha Uma Habilidade Para Treinar,,,Nome Da Habilidade,Custo Em Moedas De Platina</t>
+          <t>Escolha a perícia para treinar,,,Nome da Perícia,Custo em Moedas de Platina</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>wCraft</t>
+          <t>wSkyTravel</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
+          <t>EA 23.334</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2448,29 +2448,29 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>「Escolha uma Receita」,,,Nome Da Receita,Possuí,Habilidade De Artesanato</t>
+          <t>Escolha a coordenação para mover,,,Coordenação,Custo em Bilhetes</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Choose a recipe,,,Recipe Name,Own,Craft Skill</t>
+          <t>Choose a coordination to move,,,Coordination,Ticket Cost</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>レシピの選択,,,製作物の名前,所有,製作スキル</t>
+          <t>座標の選択,,,目的の座標,消費チケット</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ListPeopleBuySlave</t>
+          <t>wCraft</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EA 23.38</t>
+          <t>Alpha 20.40</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2480,29 +2480,29 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Escolha Um Escravo,,,Nome Da Criatura,Preço,Trabalho</t>
+          <t>Escolha a receita,,,Nome da Receita,Tenha,Fabricação</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Choose a slave,,,Creature Name,Price,Work</t>
+          <t>Choose a recipe,,,Recipe Name,Own,Craft Skill</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>売買する奴隷の選択,,,生物の名前,値段,仕事</t>
+          <t>レシピの選択,,,製作物の名前,所有,製作スキル</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ListPeopleRevive</t>
+          <t>ListPeopleBuySlave</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>EA 23.38</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Escolha Um Aliado Para Reviver,,,Nome Do Aliado,Preço,Classe</t>
+          <t>Escolha o escravo,,,Nome da Criatura,Preço,Trabalho</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Choose an ally to revive,,,Ally Name,Price,Class</t>
+          <t>Choose a slave,,,Creature Name,Price,Work</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>呼び戻す仲間の選択,,,仲間の名前,値段,クラス</t>
+          <t>売買する奴隷の選択,,,生物の名前,値段,仕事</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ListPeopleCallReserve</t>
+          <t>ListPeopleRevive</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2544,29 +2544,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Escolha Um Aliado Para Chamar,,,Nome Do Aliado,Interação,Classe</t>
+          <t>Escolha o aliado a reviver,,,Nome do Aliado,Preço,Classe</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Choose an ally to recall,,,Ally Name,Interaction,Class</t>
+          <t>Choose an ally to revive,,,Ally Name,Price,Class</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>呼び戻す仲間の選択,,,仲間の名前,アクション,クラス</t>
+          <t>呼び戻す仲間の選択,,,仲間の名前,値段,クラス</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ListPeople</t>
+          <t>ListPeopleCallReserve</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Beta 22.52</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2576,29 +2576,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>,,,Nome Do Aliado,Interação,Informação</t>
+          <t>Escolha o aliado a chamar,,,Nome do Aliado,Interação,Classe</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>,,,Ally Name,Interaction,Info</t>
+          <t>Choose an ally to recall,,,Ally Name,Interaction,Class</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>,,,仲間の名前,アクション,情報</t>
+          <t>呼び戻す仲間の選択,,,仲間の名前,アクション,クラス</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ListPeopleSelect</t>
+          <t>ListPeople</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Beta 22.52</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2608,29 +2608,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>,,,Nome Do Aliado,Nota</t>
+          <t>,,,Nome do Aliado,Interação,Info</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>,,,Ally Name,Note</t>
+          <t>,,,Ally Name,Interaction,Info</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>,,,仲間の名前,ノート</t>
+          <t>,,,仲間の名前,アクション,情報</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ListPeopleBed</t>
+          <t>ListPeopleSelect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EA 23.40</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>,,,Nome Do Aliado,Nota</t>
+          <t>,,,Nome do Aliado,Nota</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2657,12 +2657,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>wBGMLot</t>
+          <t>ListPeopleBed</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>EA 23.40</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2672,29 +2672,29 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Escolha Uma Música,,,Nome Da Música,Interação</t>
+          <t>,,,Nome do Aliado,Nota</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Choose a song,,,Song Name,Interaction</t>
+          <t>,,,Ally Name,Note</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>音楽の選択,,,曲名,アクション</t>
+          <t>,,,仲間の名前,ノート</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>wPlaylist</t>
+          <t>ListPeopleParty</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>EA 23.284</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2704,24 +2704,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Playlist Atual,,,Nome Da Música,Interação</t>
+          <t>,,,Nome do Aliado,Favorito</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Current Playlist,,,Song Name,Interaction</t>
+          <t>,,,Ally Name,Favorite</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>現在のプレイリスト,,,曲名,アクション</t>
+          <t>,,,仲間の名前,お気に入り</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>wPlaylist2</t>
+          <t>wBGMLot</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2736,29 +2736,29 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Músicas Na Memória,,,Nome Da Música,Interação</t>
+          <t>Escolha a música,,,Nome da Música,Interação</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Songs in memory,,,Song Name,Interaction</t>
+          <t>Choose a song,,,Song Name,Interaction</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>記憶の中の曲,,,曲名,アクション</t>
+          <t>音楽の選択,,,曲名,アクション</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>wTravel</t>
+          <t>wPlaylist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alpha 12.1</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,132 +2768,142 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Escolha Um Destino Para Viagem Rápida,,,Nome Do Destino,Dias,Ração Requerida</t>
+          <t>Playlist Atual,,,Nome da Música,Interação</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Choose a fast travel destination,,,Destination Name,Days,Req Ration</t>
+          <t>Current Playlist,,,Song Name,Interaction</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ファストトラベル目的地の選択,,,目的地の名前,経過日,必要旅糧</t>
+          <t>現在のプレイリスト,,,曲名,アクション</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dayLuck</t>
+          <t>wPlaylist2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>Alpha 19.1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>window</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Caranguejo Rei,Atum Bluefin,Lagosta Espinhosa,Amêijoa Oriental Comum,Ouriço-Do-Mar,Pepino-Do-Mar</t>
+          <t>Músicas na memória,,,Nome da Música,Interação</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>King Crab,Bluefin Tuna,Spiny Lobster,Common Orient Clam,Sea Urchin,Sea Cucumber</t>
+          <t>Songs in memory,,,Song Name,Interaction</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>タラバガニ,クロマグロ,イセエビ,ハマグリ,ウニ,ナマコ</t>
+          <t>記憶の中の曲,,,曲名,アクション</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dayLuck2</t>
+          <t>wTravel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alpha 14.1</t>
+          <t>Alpha 12.1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>window</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Miau Miau Miau!,Miau Miau!,Miau.,Chato.,Cuidado!,(Pssst...)</t>
+          <t>Escolha o destino da viagem rápida,,,Nome do Destino,Dias,Ração Necessária</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mew mew mew!,Mew mew!,Mewew.,Boring.,Beware!,(Pssst...)</t>
+          <t>Choose a fast travel destination,,,Destination Name,Days,Req Ration</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>うみみゃぁあ！,うみゃあ！,うみみ,つまんない,気を付けてね！,（フシュー・・・）</t>
+          <t>ファストトラベル目的地の選択,,,目的地の名前,経過日,必要旅糧</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>daggerTalk</t>
+          <t>dayLuck</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Libere-Os...!,Nossas Espadas...!,Minha Espada...!,Meu Amigo...,Minha Alma...,Meu Orgulho...,Por Favor... A Espada...,Esperamos Por Tanto Tempo...,Minha Espada Que Foi Atada Por Ele...,Minha Espada Que Foi Roubada Por Ele...,Minha Espada...,A Espada...,Você... Libertou Minha Espada...?,Quem É...?</t>
+          <t>Caranguejo Real,Atum Rabilho,Lagosta,Marisco,Ouriço-do-mar,Marisco-Bolha</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Release them...!,Our swords...!,My sword...!,My friend...,My soul...,My pride...,Please... the sword...,We have been waiting for so long...,My sword that was bound by him...,My sword that was stolen by him...,My sword...,The sword...,You...set my sword free...?,Who is it...?</t>
+          <t>King Crab,Bluefin Tuna,Spiny Lobster,Common Orient Clam,Sea Urchin,Sea Cucumber</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>解き放って…！,私たちの剣を…！,私の剣を…！,剣を…,私の友を…,私の魂を…,私の誇りを…,頼む…剣を…,この時をずっと待っていた…,奴に囚われた私の剣を…,奴に奪われた私の剣を…,剣を…,解放…してくれるのか…？,誰だ…？,13</t>
+          <t>タラバガニ,クロマグロ,イセエビ,ハマグリ,ウニ,ナマコ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>quality_furniture</t>
+          <t>dayLuck2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>Alpha 14.1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Estúpido,Sem Graça,Legal,Favorito Da Madame,Enfeitiçado,Maniaco,Estimado,Magnífico,Real,Obra-Prima,Celestial,Divino</t>
+          <t>Mew mew mew!,Mew mew!,Mewew.,Que tédio.,Cuidado!,(Psst...)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>stupid,lame,cool,madam's favorite,bewitched,maniac,esteemed,magnificent,royal,masterpiece,heavenly,godly</t>
+          <t>Mew mew mew!,Mew mew!,Mewew.,Boring.,Beware!,(Pssst...)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>愚かな,みすぼらしい,気になる,いい感じの,マダム殺しの,マニア向けの,尊い,凄く豪華な,王家御用達の,芸術的な,神々しい,世界最高の</t>
+          <t>うみみゃぁあ！,うみゃあ！,うみみ,つまんない,気を付けてね！,（フシュー・・・）</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ancientbook</t>
+          <t>daggerTalk</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2903,78 +2913,78 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Manuscrito Voynich,Cânticos Dhol,Escritura De Ponape,Revelações De Glaaki,Fragmentos De G'harne,Liber Damnatus,Livro De Dzyan,Livro De Eibon,Grande Grimório,Fragmentos De Celaeno,Necronomicon,O Texto De R'lyeh,Fragmentos De Eltdown,O Ramo Dourado,Apocalipse</t>
+          <t>Libertem-nos...!,Nossas espadas...!,Minha espada...!,Meu amigo...,Minha alma...,Meu orgulho...,Por favor... a espada...,Esperamos por tanto tempo...,Minha espada que ele aprisionou...,Minha espada que ele roubou...,Minha espada...,A espada...,Você...libertou minha espada...?,Quem foi...?</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Voynich Manuscript,Dhol Chants,Ponape Scripture,Revelations of Glaaki,G'harne Fragments,Liber Damnatus,Book of Dzyan,Book of Eibon,Grand Grimoire,Celaeno Fragments,Necronomicon,The R'lyeh Text,Eltdown Shards,The Golden Bough,Apocalypse</t>
+          <t>Release them...!,Our swords...!,My sword...!,My friend...,My soul...,My pride...,Please... the sword...,We have been waiting for so long...,My sword that was bound by him...,My sword that was stolen by him...,My sword...,The sword...,You...set my sword free...?,Who is it...?</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ヴォイニッチ写本,ドール賛歌,ポナペ教教典,グラーキ黙示録,グ＝ハーン断章,断罪の書,ドジアンの書,エイボンの書,大いなる教書,セラエノ断章,ネクロノミコン,ルルイエ異本,エルトダウン・シャールズ,金枝篇,終焉の書</t>
+          <t>解き放って…！,私たちの剣を…！,私の剣を…！,剣を…,私の友を…,私の魂を…,私の誇りを…,頼む…剣を…,この時をずっと待っていた…,奴に囚われた私の剣を…,奴に奪われた私の剣を…,剣を…,解放…してくれるのか…？,誰だ…？,13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>music_result</t>
+          <t>quality_furniture</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>É Uma Perda De Tempo.,Quase Todos Te Ignoram.,Você Precisa Praticar Muito Mais.,Você Terminou De Jogar.,Não É Bom.,As Pessoas Parecem Gostar Da Sua Performance.,Sua Performance É Um Sucesso.,Maravilhoso!,Excelente Performance.,Um Palco Lendário!</t>
+          <t>toscana,tosca,legal,favorita da madame,enfeitiçada,maníaca,estimada,magnífica,real,obra-prima,celestial,divina</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>It is a waste of time.,Almost everyone ignores you.,You need to practice lot more.,You finish playing.,Not good.,People seem to like your performance.,Your performance is successful.,Wonderful!,Great performance.,A Legendary stage!</t>
+          <t>stupid,lame,cool,madam's favorite,bewitched,maniac,esteemed,magnificent,royal,masterpiece,heavenly,godly</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>まるで駄目だ…,不評だった…,もっと練習しなくては…,演奏を終えた。,いまいちだ。,手ごたえがあった。,納得できる演奏ができた。,大盛況だ！,素晴らしい！,歴史に残る名演だ！</t>
+          <t>愚かな,みすぼらしい,気になる,いい感じの,マダム殺しの,マニア向けの,尊い,凄く豪華な,王家御用達の,芸術的な,神々しい,世界最高の</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>buff_STR</t>
+          <t>ancientbook</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Poderoso,Fraco</t>
+          <t>Manuscrito Voynich,Cânticos de Dhol,Escritura de Ponape,Revelações de Glaaki,Fragmentos de G'harne,Liber Damnatus,Livro de Dzyan,Livro de Eibon,Grand Grimório,Fragmentos de Celaeno,Necronomicon,O Texto de R'lyeh,Fragmentos de Eltdown,O Ramo de Ouro,Apocalipse</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mighty,Weakened</t>
+          <t>Voynich Manuscript,Dhol Chants,Ponape Scripture,Revelations of Glaaki,G'harne Fragments,Liber Damnatus,Book of Dzyan,Book of Eibon,Grand Grimoire,Celaeno Fragments,Necronomicon,The R'lyeh Text,Eltdown Shards,The Golden Bough,Apocalypse</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>剛力,衰弱</t>
+          <t>ヴォイニッチ写本,ドール賛歌,ポナペ教教典,グラーキ黙示録,グ＝ハーン断章,断罪の書,ドジアンの書,エイボンの書,大いなる教書,セラエノ断章,ネクロノミコン,ルルイエ異本,エルトダウン・シャールズ,金枝篇,終焉の書</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>buff_END</t>
+          <t>music_result</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2984,24 +2994,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fortificado,Frágil</t>
+          <t>É perda de tempo.,Quase todos te ignoram.,Você precisa treinar muito mais.,Você termina a apresentação.,Não foi bom.,As pessoas parecem gostar da sua apresentação.,Sua apresentação foi um sucesso.,Maravilhoso!,Ótima apresentação.,Um palco lendário!</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fortified,Fragile</t>
+          <t>It is a waste of time.,Almost everyone ignores you.,You need to practice lot more.,You finish playing.,Not good.,People seem to like your performance.,Your performance is successful.,Wonderful!,Great performance.,A Legendary stage!</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>堅牢,脆弱</t>
+          <t>まるで駄目だ…,不評だった…,もっと練習しなくては…,演奏を終えた。,いまいちだ。,手ごたえがあった。,納得できる演奏ができた。,大盛況だ！,素晴らしい！,歴史に残る名演だ！</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>buff_DEX</t>
+          <t>buff_STR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3011,24 +3021,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ágil,Desajeitado</t>
+          <t>Poderoso,Enfraquecido</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Agile,Clumsy</t>
+          <t>Mighty,Weakened</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>巧手,拙劣</t>
+          <t>剛力,衰弱</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>buff_PER</t>
+          <t>buff_END</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3038,24 +3048,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Percepção Aguçada,Percepção Limitada</t>
+          <t>Fortificado,Frágil</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Keen Sense,Dull Sense</t>
+          <t>Fortified,Fragile</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>鋭敏,鈍化</t>
+          <t>堅牢,脆弱</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>buff_LER</t>
+          <t>buff_DEX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3065,24 +3075,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Iluminado,Prejudicado</t>
+          <t>Ágil,Desengonçado</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Enlightened,Hindered</t>
+          <t>Agile,Clumsy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>学力向上,学習困難</t>
+          <t>巧手,拙劣</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>buff_WIL</t>
+          <t>buff_PER</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3092,24 +3102,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Inflexível,Subjugado</t>
+          <t>Sentidos Aguçados,Sentidos Embotados</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Unyielding,Subdued</t>
+          <t>Keen Sense,Dull Sense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>不屈,屈服</t>
+          <t>鋭敏,鈍化</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>buff_MAG</t>
+          <t>buff_LER</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3119,24 +3129,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Magia Amplificada,Magia Drenada</t>
+          <t>Iluminado,Sufocado</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Amplified Magic,Drained Magic</t>
+          <t>Enlightened,Hindered</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>魔力増幅,魔力減少</t>
+          <t>学力向上,学習困難</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>buff_CHA</t>
+          <t>buff_WIL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3146,24 +3156,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Alegre,Sombrio</t>
+          <t>Inabalável,Subjugado</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cheerful,Gloom</t>
+          <t>Unyielding,Subdued</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>陽気,陰気</t>
+          <t>不屈,屈服</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>buff_LUC</t>
+          <t>buff_MAG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3173,24 +3183,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sortudo,Amaldiçoado</t>
+          <t>Magia Amplificada,Magia Drenada</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lucky,Jinxed</t>
+          <t>Amplified Magic,Drained Magic</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>フィーバー,ジンクス</t>
+          <t>魔力増幅,魔力減少</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>buff_SPD</t>
+          <t>buff_CHA</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3200,24 +3210,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Acelerado,Lento</t>
+          <t>Alegre,Melancolia</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Haste,Slow</t>
+          <t>Cheerful,Gloom</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>加速,鈍足</t>
+          <t>陽気,陰気</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>buff_LUC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3227,272 +3237,272 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Bruto,Normal,Bom,Milagroso,Divino,Especial</t>
+          <t>Sortudo,Enfeitiçado</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>crude,normal,good,miracle,godly,special</t>
+          <t>Lucky,Jinxed</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>粗悪,普通,高品質,奇跡,神器,特別製</t>
+          <t>フィーバー,ジンクス</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>quality_food</t>
+          <t>buff_SPD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Desgastado,Qualidade Comum,Qualidade Razoável,Qualidade Fina,Qualidade Premium,Qualidade Real</t>
+          <t>Apressado,Lento</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tarnished,Common Quality,Fair Quality,Fine Quality,Premium Quality,Royal Quality</t>
+          <t>Haste,Slow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>粗悪品,普通の出来,まあまあの出来,良い出来,高級品,極上品</t>
+          <t>加速,鈍足</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>quality_general</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alpha 19.1</t>
+          <t>Alpha 17.1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>,Qualidade,Puro,Fabuloso</t>
+          <t>grosseiro,normal,bom,milagroso,divino,especial</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">,quality,pure,fabled </t>
+          <t>crude,normal,good,miracle,godly,special</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>,上質な,純粋な,幻の</t>
+          <t>粗悪,普通,高品質,奇跡,神器,特別製</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>quality_fish</t>
+          <t>quality_food</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EA 23.126</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>,vivaz ,lendário ,lendário supremo</t>
+          <t>Enferrujado,Qualidade Comum,Qualidade Decente,Qualidade Boa,Qualidade Premium,Qualidade Real</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">,lively ,fabled ,legendary </t>
+          <t>Tarnished,Common Quality,Fair Quality,Fine Quality,Premium Quality,Royal Quality</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>,ぴちぴちの,幻の,伝説の</t>
+          <t>粗悪品,普通の出来,まあまあの出来,良い出来,高級品,極上品</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>work_lv</t>
+          <t>quality_general</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>Alpha 19.1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-,Amador,Novato,Aprendiz,Profissional,Especialista,Versado,Mestre,Grande Mestre</t>
+          <t xml:space="preserve">,qualidade,pura,lendária </t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>-,Amateur,Novice,Apprentice,Journeyman,Expert,Adept,Master,Grandmaster</t>
+          <t xml:space="preserve">,quality,pure,fabled </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-,へっぽこ,初心者,見習い,職人,専門家,熟練者,達人,巨匠</t>
+          <t>,上質な,純粋な,幻の</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>civility</t>
+          <t>quality_fish</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>EA 23.126</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Mínimo,Baixo,Normal,Alto,Máximo</t>
+          <t xml:space="preserve">,vivaz ,lendária ,mítica </t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lowest,Low,Normal,High,Highest</t>
+          <t xml:space="preserve">,lively ,fabled ,legendary </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>最低,低い,普通,高い,最高</t>
+          <t>,ぴちぴちの,幻の,伝説の</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>startMode</t>
+          <t>work_lv</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EA 23.187</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Uma noite no Prado,Uma noite no Prado (Inverno),Em uma caverna,Um Bloco (Teste)</t>
+          <t>-,Amador,Novato,Aprendiz,Companheiro,Perito,Adepto,Mestre,Grão-Mestre</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>A night in the Meadow,A night in the Meadow (Winter),In a cave,One Block (Test)</t>
+          <t>-,Amateur,Novice,Apprentice,Journeyman,Expert,Adept,Master,Grandmaster</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>野原の一夜,野原の一夜 (冬),洞窟で,ワンブロック（テスト）</t>
+          <t>-,へっぽこ,初心者,見習い,職人,専門家,熟練者,達人,巨匠</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>exhint_AM_Terrain</t>
+          <t>civility</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alpha 20.40</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>extrahint</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Altura Instantânea: &lt;b&gt;Shift + Clique&lt;/b&gt;</t>
+          <t>Mínimo,Baixo,Normal,Alto,Máximo</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Instant Height: &lt;b&gt;Shift + Click&lt;/b&gt;</t>
+          <t>Lowest,Low,Normal,High,Highest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>一括変更:  &lt;b&gt;Shift + クリック&lt;/b&gt;</t>
+          <t>最低,低い,普通,高い,最高</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>guild_title</t>
+          <t>startMode</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Alpha 21.6</t>
+          <t>EA 23.187</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Novato,Aprendiz,Profissional,Veterano,Especialista,Mestre,Grande Mestre</t>
+          <t>Uma noite na Campina,Uma noite na Campina (Inverno),Numa caverna,Um Bloco (Teste)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Novice,Apprentice,Journeyman,Adept,Expert,Master,Grandmaster</t>
+          <t>A night in the Meadow,A night in the Meadow (Winter),In a cave,One Block (Test)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ノービス,アプレンティス,ジャーニーマン,アデプト,エキスパート,マスター,グランドマスター</t>
+          <t>野原の一夜,野原の一夜 (冬),洞窟で,ワンブロック（テスト）</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>plant_size</t>
+          <t>exhint_AM_Terrain</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Alpha 21.6</t>
+          <t>Alpha 20.40</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>extrahint</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Extremamente Pequeno,Pequeno,Prático,Consideravelmente Grande,Enorme,Muito Enorme,Tamanho Monstruoso,Maior Que Um Homem,Tamanho Lendário,Mais Pesado Que Um Elefante</t>
+          <t>Altura instantânea: &lt;b&gt;Shift + Clique&lt;/b&gt;</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">extremely mini ,small ,handy ,rather big ,huge ,very huge ,monstrous-size ,bigger than a man ,legendary-size ,heavier than an elephant </t>
+          <t>Instant Height: &lt;b&gt;Shift + Click&lt;/b&gt;</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>超ミニに育った,小振りに育った,手ごろに育った,やや大きく育った,どでかく育った,かなり巨大に育った,化け物サイズに育った,人より大きく育った,伝説的サイズに育った,象より重く育った</t>
+          <t>一括変更:  &lt;b&gt;Shift + クリック&lt;/b&gt;</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>num_rank</t>
+          <t>guild_title</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3502,179 +3512,368 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Th,St,Nd,Rd</t>
+          <t>Novato,Aprendiz,Companheiro,Adepto,Perito,Mestre,Grão-Mestre</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>th,st,nd,rd</t>
+          <t>Novice,Apprentice,Journeyman,Adept,Expert,Master,Grandmaster</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>位</t>
+          <t>ノービス,アプレンティス,ジャーニーマン,アデプト,エキスパート,マスター,グランドマスター</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>fur</t>
+          <t>plant_size</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EA 23.146</t>
+          <t>Alpha 21.6</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Recém-Crescido,Levemente Fofo,Quase Fofo,Fofo,*Fofo*</t>
+          <t xml:space="preserve">extremamente mini ,pequeno ,prático ,bem grande ,enorme ,muito enorme ,de tamanho monstruoso ,maior que um homem ,de tamanho lendário ,mais pesado que um elefante </t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Newly grown,Slightly fluffy,Almost fluffy,Fluffy,*Fluffy*</t>
+          <t xml:space="preserve">extremely mini ,small ,handy ,rather big ,huge ,very huge ,monstrous-size ,bigger than a man ,legendary-size ,heavier than an elephant </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>生えたて,少しもこもこ,もこもこ,ふさもこ,*ふさもこ*</t>
+          <t>超ミニに育った,小振りに育った,手ごろに育った,やや大きく育った,どでかく育った,かなり巨大に育った,化け物サイズに育った,人より大きく育った,伝説的サイズに育った,象より重く育った</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>search_words</t>
+          <t>num_rank</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EA 23.40</t>
+          <t>Alpha 21.6</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Conta,Imposto,Treinador,Guarda</t>
+          <t>º,º,º,º</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>bill,tax,trainer,guard</t>
+          <t>th,st,nd,rd</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>請求書,納税箱,トレイナー,ガード</t>
+          <t>位</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>fortuneroll</t>
+          <t>fur</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EA 23.62</t>
+          <t>EA 23.146</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Perder,3º Prêmio,2º Prêmio,1º Prêmio</t>
+          <t>Recém-crescida,Levemente fofa,Quase fofa,Fofa,*Fofa*</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lose,3rd Prize,2nd Prize,1st Prize</t>
+          <t>Newly grown,Slightly fluffy,Almost fluffy,Fluffy,*Fluffy*</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>ハズレ,3等,2等,1等</t>
+          <t>生えたて,少しもこもこ,もこもこ,ふさもこ,*ふさもこ*</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>pp_templates</t>
+          <t>search_words</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EA 23.94</t>
+          <t>EA 23.40</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Aventureiro Novato,Aventureiro,Aventureiro Veterano,Personalizado</t>
+          <t>conta,imposto,treinador,guarda</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Novice Adventurer,Adventurer,Veteran Adventurer,Custom</t>
+          <t>bill,tax,trainer,guard</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>駆け出し冒険者,冒険者,熟練冒険者,カスタム</t>
+          <t>請求書,納税箱,トレイナー,ガード</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>pp_titles</t>
+          <t>fortuneroll</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EA 23.94</t>
+          <t>EA 23.62</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Aventureiro Legado,Aventureiro Novato,Aventureiro,Aventureiro Veterano,Aventureiro Lendário,Aventureiro Mítico</t>
+          <t>Perdeu,3º Prêmio,2º Prêmio,1º Prêmio</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Legacy Adventurer,Novice Adventurer,Adventurer,Veteran Adventurer,Legendary Adventurer,Mythical Adventurer</t>
+          <t>Lose,3rd Prize,2nd Prize,1st Prize</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>レガシー冒険者,駆け出し冒険者,冒険者,熟練冒険者,伝説の冒険者,神話の冒険者</t>
+          <t>ハズレ,3等,2等,1等</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>pp_templates</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EA 23.94</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Aventureiro Novato,Aventureiro,Aventureiro Veterano,Personalizado</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Novice Adventurer,Adventurer,Veteran Adventurer,Custom</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>駆け出し冒険者,冒険者,熟練冒険者,カスタム</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>pp_titles</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EA 23.94</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Aventureiro de Legado,Aventureiro Novato,Aventureiro,Aventureiro Veterano,Aventureiro Lendário,Aventureiro Mítico</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Legacy Adventurer,Novice Adventurer,Adventurer,Veteran Adventurer,Legendary Adventurer,Mythical Adventurer</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>レガシー冒険者,駆け出し冒険者,冒険者,熟練冒険者,伝説の冒険者,神話の冒険者</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>barrel</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>EA 23.115</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Barril♪,Barril!,Barril!,Barril.</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Barr～el♪,Barril!,Barr～il!,Barril.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>Ba～rrel♪,Barrel!,Barre~l!,Barrel.</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>た～る♪,たーる！,たーるっ,たる</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>bracket_1</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EA 23.322</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>「,」</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>「,」</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>「,」</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>bracket_2</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EA 23.322</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>『,』</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>『,』</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>『,』</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>bracket_3</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EA 23.322</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>《,》</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>《,》</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>《,》</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>bracket_4</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EA 23.322</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>(,)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>(,)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>(,)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>bracket_5</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EA 23.322</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>〈,〉</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>〈,〉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>〈,〉</t>
         </is>
       </c>
     </row>
